--- a/Suporte-ThermoSafeHidraulico-v01.xlsx
+++ b/Suporte-ThermoSafeHidraulico-v01.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="261">
   <si>
     <t>A) Criar o projeto e preparar o Firestore (cloud)</t>
   </si>
@@ -3741,6 +3741,12 @@
   </si>
   <si>
     <t>pip install pandas openpyxl --upgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> git rm -r --cached .github Sigiloso</t>
+  </si>
+  <si>
+    <t>não github de diretorio sigiloso</t>
   </si>
 </sst>
 </file>
@@ -5571,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B5:C97"/>
+  <dimension ref="B5:C101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="67.42578125" customWidth="1"/>
@@ -5797,9 +5803,17 @@
     <row r="96" spans="2:2">
       <c r="B96" s="2"/>
     </row>
-    <row r="97" spans="2:2">
+    <row r="97" spans="2:3">
       <c r="B97" s="26" t="s">
         <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="B101" t="s">
+        <v>259</v>
+      </c>
+      <c r="C101" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/Suporte-ThermoSafeHidraulico-v01.xlsx
+++ b/Suporte-ThermoSafeHidraulico-v01.xlsx
@@ -9,12 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11910" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11910" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
     <sheet name="Planilha3" sheetId="3" r:id="rId3"/>
+    <sheet name="Planilha4" sheetId="4" r:id="rId4"/>
+    <sheet name="Planilha5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="718">
   <si>
     <t>A) Criar o projeto e preparar o Firestore (cloud)</t>
   </si>
@@ -3747,13 +3749,2431 @@
   </si>
   <si>
     <t>não github de diretorio sigiloso</t>
+  </si>
+  <si>
+    <t>Authentication keys</t>
+  </si>
+  <si>
+    <t>SSH</t>
+  </si>
+  <si>
+    <r>
+      <t>Meu Desktop Casa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SHA256:fen1c80359uiUq+/uo90D0kc7HhAbt1RUn0aanMgwAM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF59636E"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Added on Sep 19, 2025Never used — Read/write</t>
+    </r>
+  </si>
+  <si>
+    <t>SHA256:fen1c80359uiUq+/uo90D0kc7HhAbt1RUn0aanMgwAM</t>
+  </si>
+  <si>
+    <t>Visão: “ThermoSafe Hidráulico Console”</t>
+  </si>
+  <si>
+    <t>Arquitetura simples (local)</t>
+  </si>
+  <si>
+    <r>
+      <t>UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Streamlit (roda local no Windows, abre no navegador).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Backend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Reusa suas funções dos scripts (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>seed_firestore.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>export_readings.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) — sem duplicar.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Credenciais</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.env</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + JSON de service account (fora do Git).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Execução</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Operador preenche formulários, clica e acompanha logs na UI.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Depois, se quiser, isso pode ir para um </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cloud Run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> privado com Google OAuth. Mas local já resolve.</t>
+    </r>
+  </si>
+  <si>
+    <t>Fluxos do operador</t>
+  </si>
+  <si>
+    <r>
+      <t>Carga</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Seleciona arquivo Excel (v2/v3 com </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) e carrega coleções.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Simulação</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Informa período, frequência, número/IDs de medidores → roda e mostra progresso.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exportação</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Escolhe CSV/JSON, delimitador, filtros de datas/medidor → gera arquivos em </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>./exports</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Purge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Botão protegido com confirmação digitada (“PURGE”).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Estimador de custo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Calcula writes previstos (para evitar sustos).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Índices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Mostra link “Criar índice” quando necessário (caso o export ordenado avise).</t>
+    </r>
+  </si>
+  <si>
+    <t>Como subir o console (uma vez)</t>
+  </si>
+  <si>
+    <t>1. Criar ambiente e instalar libs:</t>
+  </si>
+  <si>
+    <t>python -m venv .venv</t>
+  </si>
+  <si>
+    <t>.\.venv\Scripts\activate</t>
+  </si>
+  <si>
+    <t>pip install streamlit pandas openpyxl python-dotenv firebase-admin google-cloud-firestore</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Garantir </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.env</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> na raiz:</t>
+    </r>
+  </si>
+  <si>
+    <t>GOOGLE_APPLICATION_CREDENTIALS=./thermosafehidraulico-firebase-adminsdk-fbsvc-1f30ae4b7a.json</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Salvar o arquivo abaixo como </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>app.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> na raiz do projeto.</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Rodar:</t>
+  </si>
+  <si>
+    <t>streamlit run app.py</t>
+  </si>
+  <si>
+    <t>Código do MVP (app.py)</t>
+  </si>
+  <si>
+    <t>O app chama suas funções internamente; se você preferir, dá para importar direto dos scripts que já tem.</t>
+  </si>
+  <si>
+    <t>Para deixá-lo autocontido, coloquei wrappers leves que reutilizam as mesmas lógicas.</t>
+  </si>
+  <si>
+    <t># app.py</t>
+  </si>
+  <si>
+    <t>from __future__ import annotations</t>
+  </si>
+  <si>
+    <t>import os, io, json, time</t>
+  </si>
+  <si>
+    <t>from datetime import datetime, timezone</t>
+  </si>
+  <si>
+    <t>from pathlib import Path</t>
+  </si>
+  <si>
+    <t>from typing import Optional, List</t>
+  </si>
+  <si>
+    <t>import streamlit as st</t>
+  </si>
+  <si>
+    <t>import pandas as pd</t>
+  </si>
+  <si>
+    <t>from dotenv import load_dotenv</t>
+  </si>
+  <si>
+    <t>import firebase_admin</t>
+  </si>
+  <si>
+    <t>from firebase_admin import credentials, firestore</t>
+  </si>
+  <si>
+    <t>from google.cloud.firestore_v1 import Increment</t>
+  </si>
+  <si>
+    <t># --- CONFIG BÁSICA ---</t>
+  </si>
+  <si>
+    <t>BASE_DIR = Path(__file__).resolve().parent</t>
+  </si>
+  <si>
+    <t>load_dotenv()</t>
+  </si>
+  <si>
+    <t>CRED_PATH = os.getenv("GOOGLE_APPLICATION_CREDENTIALS", "").strip()</t>
+  </si>
+  <si>
+    <t>if CRED_PATH and not os.path.isabs(CRED_PATH):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CRED_PATH = str((BASE_DIR / CRED_PATH).resolve())</t>
+  </si>
+  <si>
+    <t>def get_db() -&gt; firestore.Client:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if not CRED_PATH or not Path(CRED_PATH).exists():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        raise RuntimeError("Defina GOOGLE_APPLICATION_CREDENTIALS em .env e garanta o JSON no caminho.")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if not firebase_admin._apps:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        firebase_admin.initialize_app(credentials.Certificate(CRED_PATH))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return firestore.client()</t>
+  </si>
+  <si>
+    <t>def month_bucket(ts: datetime) -&gt; str:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return f"{ts.year:04d}_{ts.month:02d}"</t>
+  </si>
+  <si>
+    <t>def parse_dt(s: str) -&gt; datetime:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if "T" in s:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return datetime.fromisoformat(s).replace(tzinfo=timezone.utc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return datetime.fromisoformat(s + "T00:00:00").replace(tzinfo=timezone.utc)</t>
+  </si>
+  <si>
+    <t># ---------- AÇÕES: CARGA VIA EXCEL ----------</t>
+  </si>
+  <si>
+    <t>REQUIRED_SHEETS = ["t_localizacao", "t_condominio", "t_cliente", "t_medidor"]</t>
+  </si>
+  <si>
+    <t>def load_excel_bytes(uploaded_file) -&gt; dict[str, pd.DataFrame]:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    data = uploaded_file.read()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    xls = pd.ExcelFile(io.BytesIO(data))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    dfs = {}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for sheet in REQUIRED_SHEETS:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if sheet not in xls.sheet_names:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            raise ValueError(f"Planilha '{sheet}' ausente.")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        df = pd.read_excel(io.BytesIO(data), sheet_name=sheet, dtype=str).fillna("")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if "_id" not in df.columns:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            raise ValueError(f"'{sheet}' precisa da coluna '_id'.")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        dfs[sheet] = df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return dfs</t>
+  </si>
+  <si>
+    <t>def upsert_localizacao(db, row: dict):  # igual ao seu seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    _id = row["_id"].strip()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    doc = {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_logradouro": row.get("f_logradouro",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_numero": row.get("f_numero",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_bairro": row.get("f_bairro",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_cidade": row.get("f_cidade",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_uf": row.get("f_uf",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_cep": row.get("f_cep",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_complemento": row.get("f_complemento","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_geo": None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_created_at": datetime.now(timezone.utc),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_ativo": True,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    lat = row.get("f_geo_lat",""); lon = row.get("f_geo_lon","")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    try:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if str(lat).strip() and str(lon).strip():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            doc["f_geo"] = {"lat": float(lat), "lon": float(lon)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    except: pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    db.collection("t_localizacao").document(_id).set(doc, merge=True)</t>
+  </si>
+  <si>
+    <t>def upsert_condominio(db, row: dict):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_nome_condominio": row.get("f_nome_condominio",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_tipo": row.get("f_tipo","condominio"),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_localizacao": row.get("f_localizacao","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_nome_resp": row.get("f_nome_resp","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_fone_resp": row.get("f_fone_resp","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_email_resp": row.get("f_email_resp","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    db.collection("t_condominio").document(_id).set(doc, merge=True)</t>
+  </si>
+  <si>
+    <t>def upsert_cliente(db, row: dict):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cpf = str(row.get("f_cpf","")).replace(".","").replace("-","").strip()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_nome_cliente": row.get("f_nome_cliente",""),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_cpf": cpf,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_condominio_id": row.get("f_condominio_id","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_bloco": row.get("f_bloco","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_apto": row.get("f_apto","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_email": row.get("f_email","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_telefone": row.get("f_telefone","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    db.collection("t_cliente").document(_id).set(doc, merge=True)</t>
+  </si>
+  <si>
+    <t>def upsert_medidor(db, row: dict):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    def pbool(x):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        s = str(x).strip().lower()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return s in ("true","1","sim","yes","y","t")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_cliente_id": row.get("f_cliente_id","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_tem_valvula": pbool(row.get("f_tem_valvula", False)),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_valvula_status": row.get("f_valvula_status","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_modelo_hw": row.get("f_modelo_hw","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_fw_version": row.get("f_fw_version","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_nota_instalacao": row.get("f_nota_instalacao","") or None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_last_ts_utc": None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_last_valor_m3": None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_monthly_total_m3": {},</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    db.collection("t_medidor").document(_id).set(doc, merge=True)</t>
+  </si>
+  <si>
+    <t># ---------- SIMULAÇÃO ----------</t>
+  </si>
+  <si>
+    <t>def write_reading(db, med_id: str, cli_id: Optional[str], ts: datetime, m3_delta: float, pulsos: int):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    month = month_bucket(ts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    med_ref = db.collection("t_medidor").document(med_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    month_doc = med_ref.collection("t_leituras").document(month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    month_doc.set({"f_bucket": month, "f_created_at": ts}, merge=True)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    items_ref = month_doc.collection("items")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_medidor_id": med_id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_cliente_id": cli_id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_ts_utc": ts,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_ano_mes_ref": month.replace("_","-"),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_valor_m3": float(m3_delta),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_pulsos": int(pulsos),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_status_sensor": 1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_flag_vazamento": False,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_ingested_at": firestore.SERVER_TIMESTAMP,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_archived_at": None,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    items_ref.add(doc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    med_ref.update({</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_last_ts_utc": ts,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_last_valor_m3": float(m3_delta),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        f"f_monthly_total_m3.{month}": Increment(float(m3_delta)),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    })</t>
+  </si>
+  <si>
+    <t>def minutes_for(freq: str) -&gt; int:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return {"5m":5,"15m":15,"1h":60,"6h":360,"1d":1440}[freq]</t>
+  </si>
+  <si>
+    <t>def list_medidores(db, limit: Optional[int]=None) -&gt; list[tuple[str, Optional[str]]]:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    snaps = list(db.collection("t_medidor").stream())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if limit: snaps = snaps[:limit]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return [(s.id, (s.to_dict() or {}).get("f_cliente_id")) for s in snaps]</t>
+  </si>
+  <si>
+    <t># ---------- EXPORT (ORDENADO) ----------</t>
+  </si>
+  <si>
+    <t>def iter_items_all_sorted(db, start_dt: Optional[datetime], end_dt: Optional[datetime]):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    q = db.collection_group("items")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if start_dt: q = q.where("f_ts_utc", "&gt;=", start_dt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if end_dt:   q = q.where("f_ts_utc", "&lt;=", end_dt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    q = q.order_by("f_medidor_id").order_by("f_ts_utc")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for s in q.stream():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        d = s.to_dict() or {}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        d["_doc_id"] = s.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        yield d</t>
+  </si>
+  <si>
+    <t># ---------- UI ----------</t>
+  </si>
+  <si>
+    <t>st.set_page_config(page_title="ThermoSafe Hidráulico Console", layout="wide")</t>
+  </si>
+  <si>
+    <t>st.title("ThermoSafe Hidráulico – Console Operacional")</t>
+  </si>
+  <si>
+    <t>with st.sidebar:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.header("Status")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.write(f"Credencial: `{Path(CRED_PATH).name if CRED_PATH else 'N/D'}`")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if st.button("Testar conexão Firestore"):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        try:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            db = get_db()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            _ = list(db.collections())[:1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            st.success("Conectado ao Firestore ✅")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        except Exception as e:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            st.error(str(e))</t>
+  </si>
+  <si>
+    <t>tab1, tab2, tab3, tab4, tab5 = st.tabs(["Carga Excel", "Simulação", "Exportação", "Purge", "Estimativa de Custo"])</t>
+  </si>
+  <si>
+    <t>with tab1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.subheader("Carga a partir do Excel (_id obrigatórios)")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    f = st.file_uploader("Selecione o Template_Carga_Firestore_v2/v3.xlsx", type=["xlsx"])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if f and st.button("Carregar no Firestore"):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            dfs = load_excel_bytes(f)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            with st.spinner("Carregando t_localizacao..."):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                for _, r in dfs["t_localizacao"].iterrows():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    upsert_localizacao(db, r.to_dict())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            with st.spinner("Carregando t_condominio..."):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                for _, r in dfs["t_condominio"].iterrows():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    upsert_condominio(db, r.to_dict())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            with st.spinner("Carregando t_cliente..."):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                for _, r in dfs["t_cliente"].iterrows():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    upsert_cliente(db, r.to_dict())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            with st.spinner("Carregando t_medidor..."):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                for _, r in dfs["t_medidor"].iterrows():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    upsert_medidor(db, r.to_dict())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            st.success("Bootstrap concluído ✅")</t>
+  </si>
+  <si>
+    <t>with tab2:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.subheader("Simular leituras")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    c1, c2, c3 = st.columns(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    start = c1.text_input("Início (UTC)", value="2024-03-11")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    end   = c2.text_input("Fim (UTC)", value="2025-09-18")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    freq  = c3.selectbox("Frequência", ["5m","15m","1h","6h","1d"], index=2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    limit = st.number_input("Limitar nº de medidores", min_value=1, max_value=5000, value=5, step=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if st.button("Simular agora"):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            t0 = parse_dt(start); t1 = parse_dt(end)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            step = minutes_for(freq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            delta_min = step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            meds = list_medidores(db, limit=limit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            total = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            prog = st.progress(0, text="Gerando leituras...")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            for i, (mid, cli) in enumerate(meds, start=1):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                ts = t0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                while ts &lt;= t1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    base = 0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    noise = (os.urandom(1)[0]/255.0 - 0.5) * 0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    m3 = max(0.0, base + noise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    pulsos = int(round(m3 * 1000))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    write_reading(db, mid, cli, ts, m3, pulsos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    total += 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    ts = ts + pd.Timedelta(minutes=delta_min).to_pytimedelta()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                prog.progress(i/len(meds), text=f"{i}/{len(meds)} medidores...")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            st.success(f"Leituras geradas: {total} ✅")</t>
+  </si>
+  <si>
+    <t>with tab3:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.subheader("Exportação (ordenado por medidor, depois timestamp)")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    c1, c2, c3, c4 = st.columns(4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    outdir = c1.text_input("Pasta de saída", value=str(BASE_DIR / "exports"))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    do_csv = c2.checkbox("CSV", value=True)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    do_json = c3.checkbox("JSONL", value=False)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    delimiter = c4.text_input("Delimitador CSV", value=";")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    s1, s2 = st.columns(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    start_e = s1.text_input("Filtrar início (UTC) opcional", value="")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    end_e   = s2.text_input("Filtrar fim (UTC) opcional", value="")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if st.button("Exportar"):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Path(outdir).mkdir(exist_ok=True, parents=True)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            start_dt = parse_dt(start_e) if start_e else None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            end_dt   = parse_dt(end_e) if end_e else None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            rows = iter_items_all_sorted(db, start_dt, end_dt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            # emitir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            n = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            fieldnames = None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if do_json:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                jf = open(Path(outdir)/"leituras_all_sorted.jsonl","w",encoding="utf-8")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if do_csv:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                cf = open(Path(outdir)/"leituras_all_sorted.csv","w",newline="",encoding="utf-8")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                import csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                writer = None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            for r in rows:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                n += 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                if do_json:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    jf.write(json.dumps(r, ensure_ascii=False, default=str)+"\n")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                if do_csv:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    if fieldnames is None:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        BASE = ["f_medidor_id","f_cliente_id","f_ts_utc","f_ano_mes_ref","f_valor_m3",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                "f_pulsos","f_status_sensor","f_flag_vazamento","f_ingested_at","f_archived_at","_doc_id"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        fieldnames = BASE + [k for k in r.keys() if k not in BASE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        writer = csv.DictWriter(cf, fieldnames=fieldnames, delimiter=delimiter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        writer.writeheader()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    row = {k: (r.get(k).isoformat() if isinstance(r.get(k), datetime) else r.get(k)) for k in fieldnames}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    writer.writerow(row)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if do_json: jf.close()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if do_csv:  cf.close()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            st.success(f"Exportado {n} linhas para {outdir} ✅")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            st.caption("Se o Firestore pedir índice composto, clique no link sugerido e rode novamente.")</t>
+  </si>
+  <si>
+    <t>with tab4:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.subheader("Purge (apagar coleções)")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.warning("CUIDADO: isso apaga TODAS as coleções abaixo.")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    collections = ["t_localizacao","t_condominio","t_cliente","t_medidor"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    confirm = st.text_input('Digite "PURGE" para confirmar:')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if st.button("APAGAR TUDO", type="primary", disabled=(confirm.strip().upper()!="PURGE")):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            for col in collections:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                st.write(f"Apagando {col}...")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                # delete recursivo simples (atenção: pode levar tempo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                for doc in db.collection(col).stream():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    # remover subcoleções (leituras) se houver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    if col=="t_medidor":</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        for b in doc.reference.collection("t_leituras").stream():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                            for it in b.reference.collection("items").stream():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                it.reference.delete()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                            b.reference.delete()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    doc.reference.delete()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            st.success("Purge concluído ✅")</t>
+  </si>
+  <si>
+    <t>with tab5:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.subheader("Estimativa de custo (writes)")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    n_med = c1.number_input("Nº de medidores", min_value=1, max_value=100000, value=5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    freq = c2.selectbox("Frequência", ["5m","15m","1h","6h","1d"], index=2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    dias = c3.number_input("Dias de simulação", min_value=1, max_value=10000, value=556)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    writes_dia_por_med = {"5m":288,"15m":96,"1h":24,"6h":4,"1d":1}[freq]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    total_writes = n_med * writes_dia_por_med * dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    custo_usd = (total_writes/100000) * 0.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.write(f"**Writes/dia/medidor**: {writes_dia_por_med}  •  **Total writes**: {total_writes:,}")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.write(f"**Custo estimado (Blaze)**: ~ **US$ {custo_usd:,.2f}** (US$0,18 por 100.000 writes)")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    st.caption("O Spark (Free Tier) dá 50k writes/mês grátis.")</t>
+  </si>
+  <si>
+    <t>Próximos incrementos (se quiser)</t>
+  </si>
+  <si>
+    <r>
+      <t>Perfis de consumo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (diurno, fim de semana, drift diário) na simulação.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Coluna </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>f_m3_acumulado</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no CSV.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Botão “Criar índice”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (abre link do índice composto).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Agendador</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (apscheduler) para rotinas diárias: exportar → marcar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>f_archived_at</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → TTL limpar.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cloud Functions (HTTP)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para receber envio dos ESP32 com </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chave de dispositivo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (mais seguro do que expor Admin SDK no firmware).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se quiser, já integro o </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>perfil diurno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e o </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>acumulado no CSV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Quer que eu inclua esses dois no app?</t>
+    </r>
+  </si>
+  <si>
+    <t>se podemos fazer uso semelhante, porque não trabalhamos entao diretamente no bigquery?</t>
+  </si>
+  <si>
+    <t>ou não daria certo?</t>
+  </si>
+  <si>
+    <t>eu pensei em usar o firestore para ser um armazenamento direto, sem a necessidade de um flask.</t>
+  </si>
+  <si>
+    <t>estou pensando errado?</t>
+  </si>
+  <si>
+    <t>eu imagino que um banco de dados direto em firestore seria muito mais rapido, mas percebo que doi mais para aprender e enfrentar os problemas</t>
+  </si>
+  <si>
+    <t>eu pensei em usar o FIREBASE para descontinuar o AWS, por que vc falou que era mais barato e tao seguro quanto o outro.</t>
+  </si>
+  <si>
+    <t>pensei em criar uma estrutura paralela, para não concentrar os dados de todos os sistemas somente na aws.</t>
+  </si>
+  <si>
+    <t>se no futuro for bom com FIREBASE, eu poderia ate pensar em migrar para esta solucao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eu queria que vc replicasse uma estrutura semelhante, fornecendo endpoint, flask e tudo mais por aqui, no Firebase. </t>
+  </si>
+  <si>
+    <t>isto seria possivel?</t>
+  </si>
+  <si>
+    <t>o importante é conseguir ler as informacoes do meu esp32 e conseguir visualizar no painel.</t>
+  </si>
+  <si>
+    <t>Pensou por 4 segundos</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apoiado — vamos começar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pelo que importa para o “mundo real”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: receber o POST do ESP32 e gravar no Firestore. Assim você testa o caminho fim-a-fim antes de pensar em dashboard.</t>
+    </r>
+  </si>
+  <si>
+    <t>Vou te deixar um plano ultra direto + código + comandos de teste. Se rodar local hoje, em poucos cliques você sobe para o Cloud Run e aponta o ESP.</t>
+  </si>
+  <si>
+    <t>Plano enxuto (em 6 passos)</t>
+  </si>
+  <si>
+    <t>1. Criar mapeamento do dispositivo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Coleção: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>t_device_map</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ID do doc = id que o ESP32 envia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ex.: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TS-ABC123</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Conteúdo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "f_tipo": "hidraulico",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "f_medidor_id": "MTR-000001",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "f_cliente_id": "CLI-000001",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "f_campo_origem": "t_canal1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "f_conv_pulsos_litro": 1.0</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Assim, sem mexer no ESP, o backend sabe que </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>t_canal1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> são </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pulsos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 1 pulso = 1 litro (ajuste se precisar).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Rodar uma API Flask local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (mesma rota que seu firmware usa: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/api/temperatura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ela: (a) loga o payload bruto em </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>t_ingest_raw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; (b) se existir mapeamento, converte → grava em </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>t_medidor/&lt;MTR&gt;/t_leituras/AAAA_MM/items</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Testar com curl/Postman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> simulando o ESP32.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Verificar no Console do Firestore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se apareceu:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>t_ingest_raw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (payload)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>t_medidor/MTR-000001/t_leituras/2025_09/items/*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (leituras)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. (Opcional hoje) Deploy para Cloud Run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e pegar uma URL pública estável.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se seu ESP exige IP fixo, depois colocamos um </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Load Balancer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> com IP estático em frente ao Cloud Run.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. (Opcional) Ativar export para BigQuery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (extensão do Firebase) para ter as leituras em SQL.</t>
+    </r>
+  </si>
+  <si>
+    <t>Código pronto (API de ingestão)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Crie uma pasta </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ingest-api/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> com dois arquivos abaixo.</t>
+    </r>
+  </si>
+  <si>
+    <t>requirements.txt</t>
+  </si>
+  <si>
+    <t>flask</t>
+  </si>
+  <si>
+    <t>waitress</t>
+  </si>
+  <si>
+    <t>firebase-admin</t>
+  </si>
+  <si>
+    <t>google-cloud-firestore</t>
+  </si>
+  <si>
+    <t>pytz</t>
+  </si>
+  <si>
+    <t>app_flask_firestore.py</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mantém a rota </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/api/temperatura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (compatível com seu legado). Se preferir, adiciono também um </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/ingest_hid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> direto em m³/pulsos.</t>
+    </r>
+  </si>
+  <si>
+    <t>from flask import Flask, request, jsonify</t>
+  </si>
+  <si>
+    <t>import os, pytz</t>
+  </si>
+  <si>
+    <t># --- Firestore Admin ---</t>
+  </si>
+  <si>
+    <t>if not firebase_admin._apps:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cred_path = os.getenv("GOOGLE_APPLICATION_CREDENTIALS")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if cred_path:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        firebase_admin.initialize_app(credentials.Certificate(cred_path))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    else:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        firebase_admin.initialize_app()  # em Cloud Run usa a service account do serviço</t>
+  </si>
+  <si>
+    <t>db = firestore.client()</t>
+  </si>
+  <si>
+    <t>app = Flask(__name__)</t>
+  </si>
+  <si>
+    <t>TZ_SP = pytz.timezone("America/Sao_Paulo")</t>
+  </si>
+  <si>
+    <t>def utcnow():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return datetime.now(timezone.utc)</t>
+  </si>
+  <si>
+    <t>def write_raw(payload: dict, ip: str|None):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    db.collection("t_ingest_raw").add({"f_received_at": utcnow(), "f_source_ip": ip, "f_payload": payload})</t>
+  </si>
+  <si>
+    <t>def get_map(device_id: str) -&gt; dict|None:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    snap = db.collection("t_device_map").document(device_id).get()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return snap.to_dict() if snap.exists else None</t>
+  </si>
+  <si>
+    <t>def write_reading(map_cfg: dict, ts_sp: datetime, m3_delta: float, pulsos: int|None):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    mid = map_cfg["f_medidor_id"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cid = map_cfg.get("f_cliente_id")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ts_utc = ts_sp.astimezone(timezone.utc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    bucket = month_bucket(ts_utc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    med = db.collection("t_medidor").document(mid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    month_doc = med.collection("t_leituras").document(bucket)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    month_doc.set({"f_bucket": bucket, "f_created_at": ts_utc}, merge=True)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    month_doc.collection("items").add({</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_medidor_id": mid,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_cliente_id": cid,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_ts_utc": ts_utc,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_ano_mes_ref": f"{ts_utc.year:04d}-{ts_utc.month:02d}",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_pulsos": int(pulsos or 0),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_archived_at": None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    med.update({</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "f_last_ts_utc": ts_utc,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        f"f_monthly_total_m3.{bucket}": Increment(float(m3_delta)),</t>
+  </si>
+  <si>
+    <t>@app.post("/api/temperatura")</t>
+  </si>
+  <si>
+    <t>def receber():</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ip = request.headers.get("X-Forwarded-For", request.remote_addr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        data = request.get_json(force=True)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    except Exception:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return jsonify({"status": "erro", "mensagem": "JSON inválido"}), 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    # Log bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    try: write_raw(data, ip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    except Exception: pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    device_id = data.get("id")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if not device_id:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return jsonify({"status": "erro", "mensagem": "id ausente"}), 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    map_cfg = get_map(device_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if not map_cfg or map_cfg.get("f_tipo") != "hidraulico":</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return jsonify({"status": "ok", "mensagem": "sem mapeamento hidráulico; salvo em t_ingest_raw"}), 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    # De onde vem o valor no legado? (padrão t_canal1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    campo = (map_cfg.get("f_campo_origem") or "t_canal1").strip()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    conv  = float(map_cfg.get("f_conv_pulsos_litro") or 1.0)  # 1 pulso = 1 litro (ajuste conforme seu sensor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    raw   = data.get(campo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if raw is None:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return jsonify({"status":"erro","mensagem":f"campo '{campo}' ausente"}), 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    # tenta pulsos (int) -&gt; m³; senão tenta float (m³ direto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    pulsos = None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        pulsos = int(str(raw).replace(",", "."))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        litros = pulsos * conv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        m3 = litros / 1000.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            m3 = float(str(raw).replace(",", "."))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        except Exception:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            return jsonify({"status":"erro","mensagem":"valor inválido (nem pulsos nem m3)"}), 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    # timestamp (se não vier, usa agora SP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ts = data.get("ts") or data.get("data_hora")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if ts:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if "T" in ts:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                ts_sp = datetime.fromisoformat(ts.replace("Z","+00:00")).astimezone(TZ_SP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            else:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                ts_sp = TZ_SP.localize(datetime.strptime(ts, "%Y-%m-%d %H:%M:%S"))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            ts_sp = datetime.now(TZ_SP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ts_sp = datetime.now(TZ_SP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        write_reading(map_cfg, ts_sp, m3, pulsos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return jsonify({"status": "ok"}), 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    except Exception as e:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return jsonify({"status":"erro","mensagem":f"falha na gravação: {e}"}), 500</t>
+  </si>
+  <si>
+    <t>if __name__ == "__main__":</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    from waitress import serve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    print("Iniciando API na porta 5000…")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    serve(app, host="0.0.0.0", port=5000)</t>
+  </si>
+  <si>
+    <t>Como rodar AGORA (local)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PowerShell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dentro da pasta </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ingest-api/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t># 1) ambiente</t>
+  </si>
+  <si>
+    <t>pip install -r requirements.txt</t>
+  </si>
+  <si>
+    <t># 2) credencial (mesma do seu projeto)</t>
+  </si>
+  <si>
+    <t># No arquivo .env da raiz ou set var de ambiente:</t>
+  </si>
+  <si>
+    <t># GOOGLE_APPLICATION_CREDENTIALS=.\thermosafehidraulico-....json</t>
+  </si>
+  <si>
+    <t>$env:GOOGLE_APPLICATION_CREDENTIALS="C:\021-Repositorios\007-Hidraulico\thermosafehidraulico-....json"</t>
+  </si>
+  <si>
+    <t># 3) subir a API local</t>
+  </si>
+  <si>
+    <t>python .\app_flask_firestore.py</t>
+  </si>
+  <si>
+    <t># -&gt; vai ouvir em http://localhost:5000/api/temperatura</t>
+  </si>
+  <si>
+    <t>Teste com curl (simulando ESP32):</t>
+  </si>
+  <si>
+    <t>curl -X POST http://localhost:5000/api/temperatura `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -H "Content-Type: application/json" `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -d '{ "id":"TS-ABC123", "t_canal1": 12, "rssi_wifi": -64, "ts":"2025-09-18T22:10:00Z" }'</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se o documento </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>t_device_map/TS-ABC123</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> existir conforme o passo 1, você verá a leitura criada em </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>t_medidor/MTR-000001/t_leituras/&lt;AAAA_MM&gt;/items</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Subir para o Cloud Run (quando quiser publicar)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dentro de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ingest-api/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>gcloud run deploy ts-hidraulico-api \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --source . \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --region southamerica-east1 \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --allow-unauthenticated \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --set-env-vars PYTHONUNBUFFERED=1</t>
+  </si>
+  <si>
+    <t>Vai te dar uma URL HTTPS.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se quiser </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>domínio próprio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, use </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Custom Domains</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no Cloud Run.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>precisar de IP fixo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, colocamos um HTTPS Load Balancer com IP estático na frente (depois te passo o passo-a-passo).</t>
+    </r>
+  </si>
+  <si>
+    <t>Segurança (fácil de ativar depois)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adicionar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>X-Api-Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ou </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HMAC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por dispositivo (sem mexer no ESP? podemos validar por IP/origem nesse início).</t>
+    </r>
+  </si>
+  <si>
+    <t>Rate limit via Cloud Run/Cloud Armor quando tiver o LB.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se topar, a gente </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>roda agora local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, confirma gravação no Firestore, e em seguida publica no </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cloud Run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Depois disso, seu ESP32 pode apontar para a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>URL única</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e pronto.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3860,6 +6280,42 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF59636E"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F2328"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF59636E"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3887,10 +6343,34 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -3900,7 +6380,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3965,6 +6445,35 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5577,7 +8086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B5:C101"/>
+  <dimension ref="B5:C108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="67.42578125" customWidth="1"/>
@@ -5814,6 +8323,26 @@
       </c>
       <c r="C101" t="s">
         <v>260</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" ht="18" thickBot="1">
+      <c r="B104" s="27" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3">
+      <c r="B105" s="28" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" ht="49.5">
+      <c r="B106" s="29" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="B108" s="30" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -6514,4 +9043,2907 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId11"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L395"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="31.5">
+      <c r="A1" s="31" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="23.25">
+      <c r="A3" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="L4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="L5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2"/>
+      <c r="L6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="L7" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2"/>
+      <c r="L8" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="L9" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="2"/>
+      <c r="L10" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="L11" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="2"/>
+      <c r="L12" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="L13" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="23.25">
+      <c r="A15" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="33" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="2"/>
+      <c r="L18" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="33" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="33" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="33" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="33" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="33" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="31.5">
+      <c r="A31" s="31" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="31.5">
+      <c r="A51" s="31" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1"/>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="1"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1"/>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="1"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="1"/>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="1"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="1"/>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="1"/>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="1"/>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="1"/>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="1"/>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="1"/>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="1"/>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="1"/>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="1"/>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="1"/>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="1"/>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="1"/>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="4" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="4" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="4" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="1"/>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="1"/>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="4" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="4" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" ht="23.25">
+      <c r="A383" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="2"/>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="33" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="2"/>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="33" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="2"/>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="33" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="2"/>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="33" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="2"/>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="33" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" t="s">
+        <v>560</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A255"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="102.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="31.5">
+      <c r="A9" s="31" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="33" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="34"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="34" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="34"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="35" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="34"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="34" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="34"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="34" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="33" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="34"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="34" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="33" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="33" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="34"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="36" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="34"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="36" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="33" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="2"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="34"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="34" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="33" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="31.5">
+      <c r="A57" s="31" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="37" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1"/>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="4" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="4" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="37" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="2"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="4" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="4" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="1"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="4" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="4" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="1"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="4" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1"/>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="1"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="4" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="1"/>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="1"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="1"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="1"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="1"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1"/>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="4" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="1"/>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="4" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="1"/>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="1"/>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="4" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="4" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="1"/>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="4" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="4" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="4" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="4" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="1"/>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="4" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="4" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="1"/>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="31.5">
+      <c r="A201" s="31" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="1"/>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="1"/>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="1"/>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="32" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="1"/>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="2"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" ht="31.5">
+      <c r="A229" s="31" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1"/>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="4" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="2"/>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="2"/>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="2"/>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" ht="23.25">
+      <c r="A247" s="3" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="2"/>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="2"/>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" t="s">
+        <v>717</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>